--- a/data/Data anual 1943 a 2025.xlsx
+++ b/data/Data anual 1943 a 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariana/Library/CloudStorage/GoogleDrive-marianabarrenadrive@gmail.com/Mi unidad/TESIS UCA/UCA Proyecto de TESIS/Estadísticas/Github/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B93CEEF-1E91-BB45-A299-E6BDB059DCA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5639CC-E891-084C-B407-AED5C9E54034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4560" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{8E7617E0-A602-A546-8CDC-4EA254E85873}"/>
   </bookViews>
@@ -53,13 +53,13 @@
     <t>ipc</t>
   </si>
   <si>
-    <t>P*soja_USA</t>
+    <t>Psoja_USA</t>
   </si>
   <si>
-    <t>P*maíz_USA</t>
+    <t>Pmaíz_USA</t>
   </si>
   <si>
-    <t>P*trigo_USA</t>
+    <t>Ptrigo_USA</t>
   </si>
 </sst>
 </file>

--- a/data/Data anual 1943 a 2025.xlsx
+++ b/data/Data anual 1943 a 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariana/Library/CloudStorage/GoogleDrive-marianabarrenadrive@gmail.com/Mi unidad/TESIS UCA/UCA Proyecto de TESIS/Estadísticas/Github/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5639CC-E891-084C-B407-AED5C9E54034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99947AA7-E309-A34C-A297-16F13B978B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4560" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{8E7617E0-A602-A546-8CDC-4EA254E85873}"/>
   </bookViews>
@@ -41,9 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>Año</t>
-  </si>
-  <si>
     <t>PBIcf</t>
   </si>
   <si>
@@ -60,6 +57,9 @@
   </si>
   <si>
     <t>Ptrigo_USA</t>
+  </si>
+  <si>
+    <t>año</t>
   </si>
 </sst>
 </file>
@@ -465,25 +465,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">

--- a/data/Data anual 1943 a 2025.xlsx
+++ b/data/Data anual 1943 a 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariana/Library/CloudStorage/GoogleDrive-marianabarrenadrive@gmail.com/Mi unidad/TESIS UCA/UCA Proyecto de TESIS/Estadísticas/Github/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99947AA7-E309-A34C-A297-16F13B978B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325E96A2-D538-E34C-9020-59881AB2A52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4560" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{8E7617E0-A602-A546-8CDC-4EA254E85873}"/>
+    <workbookView xWindow="-4560" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{8E7617E0-A602-A546-8CDC-4EA254E85873}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>PBIcf</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>año</t>
+  </si>
+  <si>
+    <t>impp_usa</t>
   </si>
 </sst>
 </file>
@@ -460,10 +463,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A76B6DA-7B87-B14D-8A1F-F9349B8BB618}">
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="17">
+    <row r="1" spans="1:8" ht="17">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -485,8 +488,11 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>1943</v>
       </c>
@@ -508,8 +514,11 @@
       <c r="G2" s="4">
         <v>1.2733333333333334</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2">
+        <v>6.9723482860472243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>1944</v>
       </c>
@@ -531,8 +540,11 @@
       <c r="G3" s="4">
         <v>1.4283333333333335</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3">
+        <v>7.434174403470049</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2">
         <v>1945</v>
       </c>
@@ -554,8 +566,11 @@
       <c r="G4" s="4">
         <v>1.4858333333333331</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4">
+        <v>7.6630439837857836</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="2">
         <v>1946</v>
       </c>
@@ -577,8 +592,11 @@
       <c r="G5" s="4">
         <v>1.7358333333333331</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5">
+        <v>8.5008701260130284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2">
         <v>1947</v>
       </c>
@@ -600,8 +618,11 @@
       <c r="G6" s="4">
         <v>2.34</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6">
+        <v>10.393131120409201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="2">
         <v>1948</v>
       </c>
@@ -623,8 +644,11 @@
       <c r="G7" s="4">
         <v>2.1491666666666664</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7">
+        <v>11.537479021987874</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="2">
         <v>1949</v>
       </c>
@@ -646,8 +670,11 @@
       <c r="G8" s="4">
         <v>1.9166666666666667</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8">
+        <v>10.977565941572596</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="2">
         <v>1950</v>
       </c>
@@ -669,8 +696,11 @@
       <c r="G9" s="4">
         <v>1.9808333333333334</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9">
+        <v>11.880783392461481</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="2">
         <v>1951</v>
       </c>
@@ -692,8 +722,11 @@
       <c r="G10" s="4">
         <v>2.1191666666666666</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10">
+        <v>14.94600098597579</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="2">
         <v>1952</v>
       </c>
@@ -715,8 +748,11 @@
       <c r="G11" s="4">
         <v>2.1150000000000002</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11">
+        <v>14.149044411662073</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="2">
         <v>1953</v>
       </c>
@@ -738,8 +774,11 @@
       <c r="G12" s="4">
         <v>1.9891666666666667</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12">
+        <v>13.568696547290031</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="2">
         <v>1954</v>
       </c>
@@ -761,8 +800,11 @@
       <c r="G13" s="4">
         <v>2.0475000000000003</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13">
+        <v>13.850696565893344</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="2">
         <v>1955</v>
       </c>
@@ -784,8 +826,11 @@
       <c r="G14" s="4">
         <v>2.0241666666666664</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14">
+        <v>13.813913954771177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="2">
         <v>1956</v>
       </c>
@@ -807,8 +852,11 @@
       <c r="G15" s="4">
         <v>1.9758333333333333</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15">
+        <v>14.128609627705313</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="2">
         <v>1957</v>
       </c>
@@ -830,8 +878,11 @@
       <c r="G16" s="4">
         <v>1.9724999999999999</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16">
+        <v>14.212204605588674</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="2">
         <v>1958</v>
       </c>
@@ -853,8 +904,11 @@
       <c r="G17" s="4">
         <v>1.7933333333333332</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17">
+        <v>13.560490712012449</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="2">
         <v>1959</v>
       </c>
@@ -876,8 +930,11 @@
       <c r="G18" s="4">
         <v>1.7458333333333333</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18">
+        <v>13.311061996808199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="2">
         <v>1960</v>
       </c>
@@ -899,8 +956,11 @@
       <c r="G19" s="4">
         <v>1.7608333333333335</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19">
+        <v>13.483202941044725</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="2">
         <v>1961</v>
       </c>
@@ -922,8 +982,11 @@
       <c r="G20" s="4">
         <v>1.8083333333333331</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20">
+        <v>13.30052275528705</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="2">
         <v>1962</v>
       </c>
@@ -945,8 +1008,11 @@
       <c r="G21" s="4">
         <v>1.9583333333333333</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21">
+        <v>13.015963235199624</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="2">
         <v>1963</v>
       </c>
@@ -968,8 +1034,11 @@
       <c r="G22" s="4">
         <v>1.9400000000000002</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22">
+        <v>13.096764086592451</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="2">
         <v>1964</v>
       </c>
@@ -991,8 +1060,11 @@
       <c r="G23" s="4">
         <v>1.6016666666666666</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23">
+        <v>13.490229101965125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="2">
         <v>1965</v>
       </c>
@@ -1014,8 +1086,11 @@
       <c r="G24" s="4">
         <v>1.3475000000000001</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24">
+        <v>13.56400379243755</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="2">
         <v>1966</v>
       </c>
@@ -1037,8 +1112,11 @@
       <c r="G25" s="4">
         <v>1.551666666666667</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25">
+        <v>13.929364163988051</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="2">
         <v>1967</v>
       </c>
@@ -1060,8 +1138,11 @@
       <c r="G26" s="4">
         <v>1.4708333333333332</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26">
+        <v>14.052321981324926</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="2">
         <v>1968</v>
       </c>
@@ -1083,8 +1164,11 @@
       <c r="G27" s="4">
         <v>1.3008333333333333</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="H27">
+        <v>14.213923684145724</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="2">
         <v>1969</v>
       </c>
@@ -1106,8 +1190,11 @@
       <c r="G28" s="4">
         <v>1.2549999999999999</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28">
+        <v>14.629940020623625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="2">
         <v>1970</v>
       </c>
@@ -1129,8 +1216,11 @@
       <c r="G29" s="4">
         <v>1.3308333333333333</v>
       </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29">
+        <v>15.630009007273875</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="2">
         <v>1971</v>
       </c>
@@ -1152,8 +1242,11 @@
       <c r="G30" s="4">
         <v>1.3599999999999999</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30">
+        <v>16.438240861454727</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="2">
         <v>1972</v>
       </c>
@@ -1175,8 +1268,11 @@
       <c r="G31" s="4">
         <v>1.5733333333333335</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31">
+        <v>17.633291851947924</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="2">
         <v>1973</v>
       </c>
@@ -1198,8 +1294,11 @@
       <c r="G32" s="4">
         <v>3.1566666666666663</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32">
+        <v>20.954275657195375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="2">
         <v>1974</v>
       </c>
@@ -1221,8 +1320,11 @@
       <c r="G33" s="4">
         <v>4.4841666666666669</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="H33">
+        <v>31.033587300993851</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="2">
         <v>1975</v>
       </c>
@@ -1244,8 +1346,11 @@
       <c r="G34" s="4">
         <v>3.6775000000000002</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34">
+        <v>33.826232773745524</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="2">
         <v>1976</v>
       </c>
@@ -1267,8 +1372,11 @@
       <c r="G35" s="4">
         <v>3.1458333333333335</v>
       </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35">
+        <v>34.860895341889076</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="2">
         <v>1977</v>
       </c>
@@ -1290,8 +1398,11 @@
       <c r="G36" s="4">
         <v>2.29</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36">
+        <v>37.634671588317353</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="2">
         <v>1978</v>
       </c>
@@ -1313,8 +1424,11 @@
       <c r="G37" s="4">
         <v>2.8241666666666663</v>
       </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37">
+        <v>40.917916941169523</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="2">
         <v>1979</v>
       </c>
@@ -1336,8 +1450,11 @@
       <c r="G38" s="4">
         <v>3.5091666666666668</v>
       </c>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38">
+        <v>47.993876753423578</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="2">
         <v>1980</v>
       </c>
@@ -1359,8 +1476,11 @@
       <c r="G39" s="4">
         <v>3.8825000000000003</v>
       </c>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39">
+        <v>61.133147907170674</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="2">
         <v>1981</v>
       </c>
@@ -1382,8 +1502,11 @@
       <c r="G40" s="4">
         <v>3.875</v>
       </c>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40">
+        <v>64.403813775912027</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="2">
         <v>1982</v>
       </c>
@@ -1405,8 +1528,11 @@
       <c r="G41" s="4">
         <v>3.5216666666666665</v>
       </c>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41">
+        <v>63.108126912532697</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="2">
         <v>1983</v>
       </c>
@@ -1428,8 +1554,11 @@
       <c r="G42" s="4">
         <v>3.5833333333333335</v>
       </c>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="H42">
+        <v>60.77148773908003</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="2">
         <v>1984</v>
       </c>
@@ -1451,8 +1580,11 @@
       <c r="G43" s="4">
         <v>3.4624999999999999</v>
       </c>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="H43">
+        <v>61.815584920180775</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="2">
         <v>1985</v>
       </c>
@@ -1474,8 +1606,11 @@
       <c r="G44" s="4">
         <v>3.1966666666666668</v>
       </c>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="H44">
+        <v>60.296612213834919</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="2">
         <v>1986</v>
       </c>
@@ -1497,8 +1632,11 @@
       <c r="G45" s="4">
         <v>2.7074999999999996</v>
       </c>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="H45">
+        <v>58.324778079595077</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="2">
         <v>1987</v>
       </c>
@@ -1520,8 +1658,11 @@
       <c r="G46" s="4">
         <v>2.5525000000000002</v>
       </c>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="H46">
+        <v>62.318764284832326</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="2">
         <v>1988</v>
       </c>
@@ -1543,8 +1684,11 @@
       <c r="G47" s="4">
         <v>3.3266666666666667</v>
       </c>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="H47">
+        <v>65.764108869962186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="2">
         <v>1989</v>
       </c>
@@ -1566,8 +1710,11 @@
       <c r="G48" s="4">
         <v>3.8758333333333335</v>
       </c>
-    </row>
-    <row r="49" spans="1:7">
+      <c r="H48">
+        <v>71.82016813835736</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="2">
         <v>1990</v>
       </c>
@@ -1589,8 +1736,11 @@
       <c r="G49" s="4">
         <v>2.9808333333333334</v>
       </c>
-    </row>
-    <row r="50" spans="1:7">
+      <c r="H49">
+        <v>74.146165068363501</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="2">
         <v>1991</v>
       </c>
@@ -1612,8 +1762,11 @@
       <c r="G50" s="4">
         <v>2.7383333333333333</v>
       </c>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="H50">
+        <v>74.196294312544651</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="2">
         <v>1992</v>
       </c>
@@ -1635,8 +1788,11 @@
       <c r="G51" s="4">
         <v>3.3824999999999998</v>
       </c>
-    </row>
-    <row r="52" spans="1:7">
+      <c r="H51">
+        <v>74.807755504436315</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="2">
         <v>1993</v>
       </c>
@@ -1658,8 +1814,11 @@
       <c r="G52" s="4">
         <v>3.2058333333333335</v>
       </c>
-    </row>
-    <row r="53" spans="1:7">
+      <c r="H52">
+        <v>74.636871508379798</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="2">
         <v>1994</v>
       </c>
@@ -1681,8 +1840,11 @@
       <c r="G53" s="4">
         <v>3.5158333333333331</v>
       </c>
-    </row>
-    <row r="54" spans="1:7">
+      <c r="H53">
+        <v>75.892211633256579</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="2">
         <v>1995</v>
       </c>
@@ -1704,8 +1866,11 @@
       <c r="G54" s="4">
         <v>4.0925000000000002</v>
       </c>
-    </row>
-    <row r="55" spans="1:7">
+      <c r="H54">
+        <v>79.316464015773832</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" s="2">
         <v>1996</v>
       </c>
@@ -1727,8 +1892,11 @@
       <c r="G55" s="4">
         <v>4.7666666666666666</v>
       </c>
-    </row>
-    <row r="56" spans="1:7">
+      <c r="H55">
+        <v>80.118304304962095</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" s="2">
         <v>1997</v>
       </c>
@@ -1750,8 +1918,11 @@
       <c r="G56" s="4">
         <v>3.7124999999999999</v>
       </c>
-    </row>
-    <row r="57" spans="1:7">
+      <c r="H56">
+        <v>78.146565888925323</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" s="2">
         <v>1998</v>
       </c>
@@ -1773,8 +1944,11 @@
       <c r="G57" s="4">
         <v>2.9033333333333333</v>
       </c>
-    </row>
-    <row r="58" spans="1:7">
+      <c r="H57">
+        <v>73.434111074597411</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" s="2">
         <v>1999</v>
       </c>
@@ -1796,8 +1970,11 @@
       <c r="G58" s="4">
         <v>2.5758333333333336</v>
       </c>
-    </row>
-    <row r="59" spans="1:7">
+      <c r="H58">
+        <v>74.065067367729142</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" s="2">
         <v>2000</v>
       </c>
@@ -1819,8 +1996,11 @@
       <c r="G59" s="4">
         <v>2.5683333333333334</v>
       </c>
-    </row>
-    <row r="60" spans="1:7">
+      <c r="H59">
+        <v>78.869536641472166</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" s="2">
         <v>2001</v>
       </c>
@@ -1842,8 +2022,11 @@
       <c r="G60" s="4">
         <v>2.8299999999999996</v>
       </c>
-    </row>
-    <row r="61" spans="1:7">
+      <c r="H60">
+        <v>76.07624055208673</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="2">
         <v>2002</v>
       </c>
@@ -1865,8 +2048,11 @@
       <c r="G61" s="4">
         <v>3.4058333333333337</v>
       </c>
-    </row>
-    <row r="62" spans="1:7">
+      <c r="H61">
+        <v>74.196516595464928</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="2">
         <v>2003</v>
       </c>
@@ -1888,8 +2074,11 @@
       <c r="G62" s="4">
         <v>3.4449999999999998</v>
       </c>
-    </row>
-    <row r="63" spans="1:7">
+      <c r="H62">
+        <v>76.385146237265829</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" s="2">
         <v>2004</v>
       </c>
@@ -1911,8 +2100,11 @@
       <c r="G63" s="4">
         <v>3.5683333333333334</v>
       </c>
-    </row>
-    <row r="64" spans="1:7">
+      <c r="H63">
+        <v>80.69010844561285</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" s="2">
         <v>2005</v>
       </c>
@@ -1934,8 +2126,11 @@
       <c r="G64" s="4">
         <v>3.3591666666666673</v>
       </c>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="H64">
+        <v>86.749917844232627</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" s="2">
         <v>2006</v>
       </c>
@@ -1957,8 +2152,11 @@
       <c r="G65" s="4">
         <v>4.0333333333333332</v>
       </c>
-    </row>
-    <row r="66" spans="1:7">
+      <c r="H65">
+        <v>90.976010515938171</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="2">
         <v>2007</v>
       </c>
@@ -1980,8 +2178,11 @@
       <c r="G66" s="4">
         <v>5.7591666666666663</v>
       </c>
-    </row>
-    <row r="67" spans="1:7">
+      <c r="H66">
+        <v>94.814327965823168</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="2">
         <v>2008</v>
       </c>
@@ -2003,8 +2204,11 @@
       <c r="G67" s="4">
         <v>8.019166666666667</v>
       </c>
-    </row>
-    <row r="68" spans="1:7">
+      <c r="H67">
+        <v>105.72461386789327</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="2">
         <v>2009</v>
       </c>
@@ -2026,8 +2230,11 @@
       <c r="G68" s="4">
         <v>5.3041666666666663</v>
       </c>
-    </row>
-    <row r="69" spans="1:7">
+      <c r="H68">
+        <v>93.572132763719978</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="2">
         <v>2010</v>
       </c>
@@ -2049,8 +2256,11 @@
       <c r="G69" s="4">
         <v>5.1150000000000002</v>
       </c>
-    </row>
-    <row r="70" spans="1:7">
+      <c r="H69">
+        <v>100.00000000000009</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="2">
         <v>2011</v>
       </c>
@@ -2072,8 +2282,11 @@
       <c r="G70" s="4">
         <v>7.4366666666666674</v>
       </c>
-    </row>
-    <row r="71" spans="1:7">
+      <c r="H70">
+        <v>110.90371344068376</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="2">
         <v>2012</v>
       </c>
@@ -2095,8 +2308,11 @@
       <c r="G71" s="4">
         <v>7.5983333333333327</v>
       </c>
-    </row>
-    <row r="72" spans="1:7">
+      <c r="H71">
+        <v>111.21261912586274</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" s="2">
         <v>2013</v>
       </c>
@@ -2118,8 +2334,11 @@
       <c r="G72" s="4">
         <v>7.315833333333333</v>
       </c>
-    </row>
-    <row r="73" spans="1:7">
+      <c r="H72">
+        <v>109.99014130791974</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="2">
         <v>2014</v>
       </c>
@@ -2141,8 +2360,11 @@
       <c r="G73" s="4">
         <v>6.3333333333333339</v>
       </c>
-    </row>
-    <row r="74" spans="1:7">
+      <c r="H73">
+        <v>108.807098258298</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" s="2">
         <v>2015</v>
       </c>
@@ -2164,8 +2386,11 @@
       <c r="G74" s="4">
         <v>5.2758333333333338</v>
       </c>
-    </row>
-    <row r="75" spans="1:7">
+      <c r="H74">
+        <v>97.739073282944503</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" s="2">
         <v>2016</v>
       </c>
@@ -2187,8 +2412,11 @@
       <c r="G75" s="4">
         <v>4.1091666666666669</v>
       </c>
-    </row>
-    <row r="76" spans="1:7">
+      <c r="H75">
+        <v>94.485704896483796</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" s="2">
         <v>2017</v>
       </c>
@@ -2210,8 +2438,11 @@
       <c r="G76" s="4">
         <v>4.4366666666666674</v>
       </c>
-    </row>
-    <row r="77" spans="1:7">
+      <c r="H76">
+        <v>97.226421294774923</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="2">
         <v>2018</v>
       </c>
@@ -2233,8 +2464,11 @@
       <c r="G77" s="4">
         <v>5.1433333333333326</v>
       </c>
-    </row>
-    <row r="78" spans="1:7">
+      <c r="H77">
+        <v>100.26947091685859</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" s="2">
         <v>2019</v>
       </c>
@@ -2256,8 +2490,11 @@
       <c r="G78" s="4">
         <v>4.7433333333333332</v>
       </c>
-    </row>
-    <row r="79" spans="1:7">
+      <c r="H78">
+        <v>98.994413407821256</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" s="2">
         <v>2020</v>
       </c>
@@ -2279,8 +2516,11 @@
       <c r="G79" s="4">
         <v>4.8574999999999999</v>
       </c>
-    </row>
-    <row r="80" spans="1:7">
+      <c r="H79">
+        <v>96.523167926388467</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" s="2">
         <v>2021</v>
       </c>
@@ -2302,8 +2542,11 @@
       <c r="G80" s="4">
         <v>6.84</v>
       </c>
-    </row>
-    <row r="81" spans="1:7">
+      <c r="H80">
+        <v>105.060795267828</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" s="2">
         <v>2022</v>
       </c>
@@ -2325,8 +2568,11 @@
       <c r="G81" s="4">
         <v>9.3000000000000007</v>
       </c>
-    </row>
-    <row r="82" spans="1:7">
+      <c r="H81">
+        <v>113.95333552415376</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" s="2">
         <v>2023</v>
       </c>
@@ -2348,8 +2594,11 @@
       <c r="G82" s="4">
         <v>7.6691666666666674</v>
       </c>
-    </row>
-    <row r="83" spans="1:7">
+      <c r="H82">
+        <v>110.43049622083474</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" s="2">
         <v>2024</v>
       </c>
@@ -2372,7 +2621,7 @@
         <v>5.7991666666666672</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:8">
       <c r="A84" s="2">
         <v>2025</v>
       </c>
